--- a/kanban.xlsx
+++ b/kanban.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD79268A-DB31-4542-8D36-30FCBD0200DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="225" windowWidth="14805" windowHeight="7890"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="kanban" sheetId="18" r:id="rId1"/>
@@ -17,17 +18,28 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">kanban!$A$3:$L$219</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">Sheet1!$C$6:$D$24</definedName>
   </definedNames>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="C21" authorId="0">
+    <comment ref="C21" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
       <text>
         <r>
           <rPr>
@@ -51,7 +63,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C34" authorId="0">
+    <comment ref="C34" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
       <text>
         <r>
           <rPr>
@@ -75,7 +87,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C60" authorId="0">
+    <comment ref="C60" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000003000000}">
       <text>
         <r>
           <rPr>
@@ -99,7 +111,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C61" authorId="0">
+    <comment ref="C61" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000004000000}">
       <text>
         <r>
           <rPr>
@@ -123,7 +135,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C62" authorId="0">
+    <comment ref="C62" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000005000000}">
       <text>
         <r>
           <rPr>
@@ -147,7 +159,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C64" authorId="0">
+    <comment ref="C64" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000006000000}">
       <text>
         <r>
           <rPr>
@@ -171,7 +183,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C65" authorId="0">
+    <comment ref="C65" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000007000000}">
       <text>
         <r>
           <rPr>
@@ -195,7 +207,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C66" authorId="0">
+    <comment ref="C66" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000008000000}">
       <text>
         <r>
           <rPr>
@@ -219,7 +231,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C67" authorId="0">
+    <comment ref="C67" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000009000000}">
       <text>
         <r>
           <rPr>
@@ -243,7 +255,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C74" authorId="0">
+    <comment ref="C74" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000A000000}">
       <text>
         <r>
           <rPr>
@@ -267,7 +279,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C75" authorId="0">
+    <comment ref="C75" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000B000000}">
       <text>
         <r>
           <rPr>
@@ -292,7 +304,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C103" authorId="0">
+    <comment ref="C103" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000C000000}">
       <text>
         <r>
           <rPr>
@@ -316,7 +328,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C114" authorId="0">
+    <comment ref="C114" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000D000000}">
       <text>
         <r>
           <rPr>
@@ -340,7 +352,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C115" authorId="0">
+    <comment ref="C115" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000E000000}">
       <text>
         <r>
           <rPr>
@@ -364,7 +376,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C144" authorId="0">
+    <comment ref="C144" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000F000000}">
       <text>
         <r>
           <rPr>
@@ -388,7 +400,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C145" authorId="0">
+    <comment ref="C145" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000010000000}">
       <text>
         <r>
           <rPr>
@@ -412,7 +424,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C146" authorId="0">
+    <comment ref="C146" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000011000000}">
       <text>
         <r>
           <rPr>
@@ -436,7 +448,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C148" authorId="0">
+    <comment ref="C148" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000012000000}">
       <text>
         <r>
           <rPr>
@@ -460,7 +472,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C152" authorId="0">
+    <comment ref="C152" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000013000000}">
       <text>
         <r>
           <rPr>
@@ -489,7 +501,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3061" uniqueCount="1010">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3061" uniqueCount="1011">
   <si>
     <t>NO</t>
   </si>
@@ -3371,12 +3383,6 @@
     <t>PAPER GUIDE,SUPPORT,LEFT:CH81:IEI </t>
   </si>
   <si>
-    <t>2026/08/07 09:28:38 </t>
-  </si>
-  <si>
-    <t>2026/08/07 18:28:38 </t>
-  </si>
-  <si>
     <t>0002727264 </t>
   </si>
   <si>
@@ -3588,12 +3594,21 @@
   </si>
   <si>
     <t>page 8 </t>
+  </si>
+  <si>
+    <t>2026/08/09 18:28:38 </t>
+  </si>
+  <si>
+    <t>2026/08/09 07:21:22 </t>
+  </si>
+  <si>
+    <t>2026/08/08 09:28:38 </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="14">
     <font>
       <sz val="11"/>
@@ -4014,6 +4029,9 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
@@ -4061,7 +4079,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -4094,9 +4112,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -4129,6 +4164,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -4304,7 +4356,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N266"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -4428,7 +4480,7 @@
         <v>706</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>652</v>
+        <v>590</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>703</v>
@@ -4489,7 +4541,7 @@
         <v>931</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>217</v>
+        <v>634</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>932</v>
@@ -4549,13 +4601,13 @@
         <v>936</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>937</v>
+        <v>1010</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>217</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>938</v>
+        <v>1008</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>198</v>
@@ -4612,7 +4664,7 @@
         <v>196</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>740</v>
+        <v>1009</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>197</v>
@@ -5158,7 +5210,7 @@
         <v>467</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>202</v>
@@ -5167,7 +5219,7 @@
         <v>203</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>634</v>
@@ -7507,7 +7559,7 @@
         <v>606</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="C89" s="3" t="s">
         <v>625</v>
@@ -7516,7 +7568,7 @@
         <v>626</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="F89" s="3" t="s">
         <v>495</v>
@@ -7547,7 +7599,7 @@
         <v>466</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="C90" s="3" t="s">
         <v>202</v>
@@ -7556,10 +7608,10 @@
         <v>203</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="G90" s="3" t="s">
         <v>758</v>
@@ -7585,16 +7637,16 @@
         <v>469</v>
       </c>
       <c r="B91" s="3" t="s">
+        <v>943</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>944</v>
+      </c>
+      <c r="D91" s="3" t="s">
         <v>945</v>
       </c>
-      <c r="C91" s="3" t="s">
+      <c r="E91" s="3" t="s">
         <v>946</v>
-      </c>
-      <c r="D91" s="3" t="s">
-        <v>947</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>948</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>634</v>
@@ -7625,7 +7677,7 @@
         <v>476</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="C92" s="3" t="s">
         <v>721</v>
@@ -7634,7 +7686,7 @@
         <v>722</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="F92" s="3" t="s">
         <v>904</v>
@@ -8700,7 +8752,7 @@
         <v>635</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="C120" s="3" t="s">
         <v>375</v>
@@ -8709,7 +8761,7 @@
         <v>665</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="F120" s="3" t="s">
         <v>197</v>
@@ -8738,7 +8790,7 @@
         <v>638</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="C121" s="3" t="s">
         <v>293</v>
@@ -8747,10 +8799,10 @@
         <v>594</v>
       </c>
       <c r="E121" s="3" t="s">
+        <v>950</v>
+      </c>
+      <c r="F121" s="3" t="s">
         <v>952</v>
-      </c>
-      <c r="F121" s="3" t="s">
-        <v>954</v>
       </c>
       <c r="G121" s="3" t="s">
         <v>843</v>
@@ -8776,16 +8828,16 @@
         <v>693</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="C122" s="3" t="s">
         <v>359</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="F122" s="3" t="s">
         <v>197</v>
@@ -8816,16 +8868,16 @@
         <v>695</v>
       </c>
       <c r="B123" s="3" t="s">
+        <v>956</v>
+      </c>
+      <c r="C123" s="3" t="s">
+        <v>957</v>
+      </c>
+      <c r="D123" s="3" t="s">
         <v>958</v>
       </c>
-      <c r="C123" s="3" t="s">
-        <v>959</v>
-      </c>
-      <c r="D123" s="3" t="s">
-        <v>960</v>
-      </c>
       <c r="E123" s="3" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="F123" s="3" t="s">
         <v>403</v>
@@ -10171,7 +10223,7 @@
         <v>461</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="C159" s="3" t="s">
         <v>500</v>
@@ -10180,7 +10232,7 @@
         <v>501</v>
       </c>
       <c r="E159" s="3" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="F159" s="3" t="s">
         <v>281</v>
@@ -10209,7 +10261,7 @@
         <v>463</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="C160" s="3" t="s">
         <v>243</v>
@@ -10218,7 +10270,7 @@
         <v>380</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="F160" s="3" t="s">
         <v>591</v>
@@ -10247,16 +10299,16 @@
         <v>464</v>
       </c>
       <c r="B161" s="3" t="s">
+        <v>962</v>
+      </c>
+      <c r="C161" s="3" t="s">
+        <v>963</v>
+      </c>
+      <c r="D161" s="3" t="s">
         <v>964</v>
       </c>
-      <c r="C161" s="3" t="s">
-        <v>965</v>
-      </c>
-      <c r="D161" s="3" t="s">
-        <v>966</v>
-      </c>
       <c r="E161" s="3" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="F161" s="3" t="s">
         <v>482</v>
@@ -10285,7 +10337,7 @@
         <v>465</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="C162" s="3" t="s">
         <v>278</v>
@@ -10294,7 +10346,7 @@
         <v>279</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="F162" s="3" t="s">
         <v>590</v>
@@ -10323,19 +10375,19 @@
         <v>468</v>
       </c>
       <c r="B163" s="3" t="s">
+        <v>966</v>
+      </c>
+      <c r="C163" s="3" t="s">
+        <v>967</v>
+      </c>
+      <c r="D163" s="3" t="s">
         <v>968</v>
       </c>
-      <c r="C163" s="3" t="s">
+      <c r="E163" s="3" t="s">
+        <v>946</v>
+      </c>
+      <c r="F163" s="3" t="s">
         <v>969</v>
-      </c>
-      <c r="D163" s="3" t="s">
-        <v>970</v>
-      </c>
-      <c r="E163" s="3" t="s">
-        <v>948</v>
-      </c>
-      <c r="F163" s="3" t="s">
-        <v>971</v>
       </c>
       <c r="G163" s="3" t="s">
         <v>884</v>
@@ -10361,7 +10413,7 @@
         <v>470</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="C164" s="3" t="s">
         <v>200</v>
@@ -10370,10 +10422,10 @@
         <v>201</v>
       </c>
       <c r="E164" s="3" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="F164" s="3" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="G164" s="3" t="s">
         <v>884</v>
@@ -10399,7 +10451,7 @@
         <v>471</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="C165" s="3" t="s">
         <v>330</v>
@@ -10408,7 +10460,7 @@
         <v>331</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="F165" s="3" t="s">
         <v>374</v>
@@ -10437,7 +10489,7 @@
         <v>472</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="C166" s="3" t="s">
         <v>202</v>
@@ -10446,7 +10498,7 @@
         <v>203</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="F166" s="3" t="s">
         <v>717</v>
@@ -10475,7 +10527,7 @@
         <v>473</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="C167" s="3" t="s">
         <v>292</v>
@@ -10484,7 +10536,7 @@
         <v>401</v>
       </c>
       <c r="E167" s="3" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="F167" s="3" t="s">
         <v>402</v>
@@ -10513,16 +10565,16 @@
         <v>474</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="C168" s="3" t="s">
+        <v>944</v>
+      </c>
+      <c r="D168" s="3" t="s">
+        <v>945</v>
+      </c>
+      <c r="E168" s="3" t="s">
         <v>946</v>
-      </c>
-      <c r="D168" s="3" t="s">
-        <v>947</v>
-      </c>
-      <c r="E168" s="3" t="s">
-        <v>948</v>
       </c>
       <c r="F168" s="3" t="s">
         <v>634</v>
@@ -10551,7 +10603,7 @@
         <v>475</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="C169" s="3" t="s">
         <v>658</v>
@@ -10560,7 +10612,7 @@
         <v>659</v>
       </c>
       <c r="E169" s="3" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="F169" s="3" t="s">
         <v>731</v>
@@ -10589,7 +10641,7 @@
         <v>477</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="C170" s="3" t="s">
         <v>270</v>
@@ -10598,7 +10650,7 @@
         <v>271</v>
       </c>
       <c r="E170" s="3" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="F170" s="3" t="s">
         <v>591</v>
@@ -10627,7 +10679,7 @@
         <v>618</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="C171" s="3" t="s">
         <v>729</v>
@@ -10636,7 +10688,7 @@
         <v>730</v>
       </c>
       <c r="E171" s="3" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="F171" s="3" t="s">
         <v>226</v>
@@ -10665,7 +10717,7 @@
         <v>619</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="C172" s="3" t="s">
         <v>719</v>
@@ -10674,10 +10726,10 @@
         <v>720</v>
       </c>
       <c r="E172" s="3" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="F172" s="3" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="G172" s="3" t="s">
         <v>884</v>
@@ -10703,16 +10755,16 @@
         <v>620</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="C173" s="3" t="s">
         <v>352</v>
       </c>
       <c r="D173" s="3" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="E173" s="3" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="F173" s="3" t="s">
         <v>614</v>
@@ -10741,7 +10793,7 @@
         <v>624</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="C174" s="3" t="s">
         <v>294</v>
@@ -10750,7 +10802,7 @@
         <v>570</v>
       </c>
       <c r="E174" s="3" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="F174" s="3" t="s">
         <v>385</v>
@@ -10779,7 +10831,7 @@
         <v>637</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="C175" s="3" t="s">
         <v>293</v>
@@ -10788,10 +10840,10 @@
         <v>594</v>
       </c>
       <c r="E175" s="3" t="s">
+        <v>950</v>
+      </c>
+      <c r="F175" s="3" t="s">
         <v>952</v>
-      </c>
-      <c r="F175" s="3" t="s">
-        <v>954</v>
       </c>
       <c r="G175" s="3" t="s">
         <v>884</v>
@@ -10817,7 +10869,7 @@
         <v>639</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="C176" s="3" t="s">
         <v>269</v>
@@ -10826,7 +10878,7 @@
         <v>613</v>
       </c>
       <c r="E176" s="3" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="F176" s="3" t="s">
         <v>197</v>
@@ -10855,7 +10907,7 @@
         <v>640</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="C177" s="3" t="s">
         <v>268</v>
@@ -10864,7 +10916,7 @@
         <v>704</v>
       </c>
       <c r="E177" s="3" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="F177" s="3" t="s">
         <v>197</v>
@@ -10893,7 +10945,7 @@
         <v>641</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="C178" s="3" t="s">
         <v>667</v>
@@ -10902,7 +10954,7 @@
         <v>668</v>
       </c>
       <c r="E178" s="3" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="F178" s="3" t="s">
         <v>669</v>
@@ -10931,7 +10983,7 @@
         <v>642</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="C179" s="3" t="s">
         <v>298</v>
@@ -10940,7 +10992,7 @@
         <v>533</v>
       </c>
       <c r="E179" s="3" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="F179" s="3" t="s">
         <v>629</v>
@@ -10969,16 +11021,16 @@
         <v>643</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="C180" s="3" t="s">
         <v>295</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="E180" s="3" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="F180" s="3" t="s">
         <v>440</v>
@@ -11007,16 +11059,16 @@
         <v>644</v>
       </c>
       <c r="B181" s="3" t="s">
+        <v>992</v>
+      </c>
+      <c r="C181" s="3" t="s">
+        <v>993</v>
+      </c>
+      <c r="D181" s="3" t="s">
         <v>994</v>
       </c>
-      <c r="C181" s="3" t="s">
-        <v>995</v>
-      </c>
-      <c r="D181" s="3" t="s">
-        <v>996</v>
-      </c>
       <c r="E181" s="3" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="F181" s="3" t="s">
         <v>842</v>
@@ -11045,19 +11097,19 @@
         <v>645</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="C182" s="3" t="s">
         <v>353</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="E182" s="3" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="F182" s="3" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="G182" s="3" t="s">
         <v>884</v>
@@ -11085,7 +11137,7 @@
         <v>646</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="C183" s="3" t="s">
         <v>354</v>
@@ -11094,7 +11146,7 @@
         <v>334</v>
       </c>
       <c r="E183" s="3" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="F183" s="3" t="s">
         <v>214</v>
@@ -11125,7 +11177,7 @@
         <v>647</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="C184" s="3" t="s">
         <v>327</v>
@@ -11134,7 +11186,7 @@
         <v>732</v>
       </c>
       <c r="E184" s="3" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="F184" s="3" t="s">
         <v>281</v>
@@ -11165,7 +11217,7 @@
         <v>694</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="C185" s="3" t="s">
         <v>572</v>
@@ -11174,7 +11226,7 @@
         <v>573</v>
       </c>
       <c r="E185" s="3" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="F185" s="3" t="s">
         <v>403</v>
@@ -11205,7 +11257,7 @@
         <v>696</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="C186" s="3" t="s">
         <v>297</v>
@@ -11214,7 +11266,7 @@
         <v>571</v>
       </c>
       <c r="E186" s="3" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="F186" s="3" t="s">
         <v>733</v>
@@ -11245,7 +11297,7 @@
         <v>697</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="C187" s="3" t="s">
         <v>355</v>
@@ -11254,7 +11306,7 @@
         <v>597</v>
       </c>
       <c r="E187" s="3" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="F187" s="3" t="s">
         <v>482</v>
@@ -11285,7 +11337,7 @@
         <v>698</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="C188" s="3" t="s">
         <v>595</v>
@@ -11294,7 +11346,7 @@
         <v>596</v>
       </c>
       <c r="E188" s="3" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="F188" s="3" t="s">
         <v>734</v>
@@ -11325,19 +11377,19 @@
         <v>699</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="C189" s="3" t="s">
         <v>296</v>
       </c>
       <c r="D189" s="3" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="E189" s="3" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="F189" s="3" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="G189" s="3" t="s">
         <v>884</v>
@@ -11456,7 +11508,7 @@
     </row>
     <row r="194" spans="1:14" ht="15" customHeight="1">
       <c r="A194" s="60" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="B194" s="60"/>
       <c r="C194" s="60"/>
@@ -12531,7 +12583,7 @@
       <c r="K266"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:L227"/>
+  <autoFilter ref="A5:L227" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="7">
     <mergeCell ref="A194:J194"/>
     <mergeCell ref="A195:J195"/>
@@ -12549,7 +12601,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor rgb="FF00B0F0"/>
     <pageSetUpPr fitToPage="1"/>
@@ -22865,7 +22917,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A6:E155"/>
+  <autoFilter ref="A6:E155" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A4:E5"/>
   </mergeCells>
@@ -22878,7 +22930,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="C6:D24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -23039,7 +23091,7 @@
       </c>
     </row>
   </sheetData>
-  <sortState ref="C6:D24">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C6:D24">
     <sortCondition ref="C6"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
